--- a/Configs/source/Datas/ghost.xlsx
+++ b/Configs/source/Datas/ghost.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>prefab_path</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
   </si>
   <si>
     <t>我是水鬼</t>
+  </si>
+  <si>
+    <t>Ghost/死水鬼.prefab</t>
   </si>
   <si>
     <t>拔舌鬼</t>
@@ -1059,18 +1065,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
     <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
+    <col min="4" max="4" width="19.9464285714286" customWidth="1"/>
     <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
     <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,44 +1086,56 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Configs/source/Datas/ghost.xlsx
+++ b/Configs/source/Datas/ghost.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="GhostTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -62,16 +62,69 @@
     <t>水鬼</t>
   </si>
   <si>
-    <t>我是水鬼</t>
-  </si>
-  <si>
-    <t>Ghost/死水鬼.prefab</t>
+    <t>水鬼，在地府中最常见的鬼怪。
+弱的一批，随便打打就能过——你该不会打不过吧？</t>
+  </si>
+  <si>
+    <t>Ghost/水鬼.prefab</t>
   </si>
   <si>
     <t>拔舌鬼</t>
   </si>
   <si>
-    <t>我是拔舌鬼</t>
+    <t>在拔舌地狱中遭遇极刑的鬼怪。
+它的攻击连续不断，而且招惹它时会增加它的力量。</t>
+  </si>
+  <si>
+    <t>Ghost/拔舌鬼.prefab</t>
+  </si>
+  <si>
+    <t>穷鬼</t>
+  </si>
+  <si>
+    <t>“叮铃铛铛”，当铜钱在地狱中回响，鬼差们最不愿意面对的穷鬼登场。
+它会不停吸取敌人的生命，将敌人的财运化为己用。</t>
+  </si>
+  <si>
+    <t>Ghost/穷鬼.prefab</t>
+  </si>
+  <si>
+    <t>铜柱鬼</t>
+  </si>
+  <si>
+    <t>巨大而沉重的铜柱是它的特征。
+如果有办法绕过铜柱的防御直接攻击其本体，或许就能一击必杀？</t>
+  </si>
+  <si>
+    <t>Ghost/铜柱鬼.prefab</t>
+  </si>
+  <si>
+    <t>肉山鬼</t>
+  </si>
+  <si>
+    <t>一动不动，无法挪移的肉山鬼。
+要想个办法撼动它才行……</t>
+  </si>
+  <si>
+    <t>Ghost/肉山鬼.prefab</t>
+  </si>
+  <si>
+    <t>阎王</t>
+  </si>
+  <si>
+    <t>什么？是阎王？你真的能战胜对手吗？</t>
+  </si>
+  <si>
+    <t>Ghost/阎王.prefab</t>
+  </si>
+  <si>
+    <t>黑白无常</t>
+  </si>
+  <si>
+    <t>鬼魂们最怕遭遇的鬼差，白无常勾魂，黑无常索命。</t>
+  </si>
+  <si>
+    <t>Ghost/黑白无常.prefab</t>
   </si>
 </sst>
 </file>
@@ -727,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -742,6 +795,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1066,13 +1122,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="19.9464285714286" customWidth="1"/>
-    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
-    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
+    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
+    <col min="3" max="3" width="20.975" customWidth="1"/>
+    <col min="4" max="4" width="19.95" customWidth="1"/>
+    <col min="5" max="5" width="11.6083333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.4166666666667" customWidth="1"/>
     <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1104,12 +1160,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+    <row r="3" s="3" customFormat="1" spans="1:4">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+    <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1117,80 +1173,119 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
+    <row r="5" ht="52" spans="1:4">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
+    <row r="6" ht="52" spans="1:4">
       <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="2:3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="65" spans="1:4">
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="65" spans="1:4">
+      <c r="B8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="39" spans="1:4">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="26" spans="1:4">
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="26" spans="1:4">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="5"/>
+    <row r="13" spans="1:4">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" s="6"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="B15" s="6"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" s="6"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="5"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
+      <c r="B18" s="6"/>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
+      <c r="B19" s="6"/>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="5"/>
+      <c r="B21" s="6"/>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="5"/>
+      <c r="B22" s="6"/>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="5"/>
+      <c r="B23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
